--- a/output/pdf_financials_xlsx/NBY.xlsx
+++ b/output/pdf_financials_xlsx/NBY.xlsx
@@ -2670,22 +2670,22 @@
         <v>12.200029</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>4.974737</v>
+        <v>1.659611</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.374545</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.274943</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.264796</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.069343</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.281637</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>2.281637</v>
@@ -2796,22 +2796,22 @@
         <v>12.200029</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>4.974737</v>
+        <v>1.659611</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.374545</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.274943</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.264796</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.069343</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.281637</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>2.281637</v>
@@ -3552,22 +3552,22 @@
         <v>5.21098</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.432092</v>
+        <v>3.747218</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.600947</v>
+        <v>3.226402</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.138295</v>
+        <v>1.863352</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.123682</v>
+        <v>0.858886</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.511771</v>
+        <v>0.442428</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.43747</v>
+        <v>0.155833</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.20755</v>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">

--- a/output/pdf_financials_xlsx/NBY.xlsx
+++ b/output/pdf_financials_xlsx/NBY.xlsx
@@ -2297,31 +2297,31 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.008796999999999999</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.006686</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.008854000000000001</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.014026</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.014967</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.018189</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.122451</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.115829</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.09506299999999999</v>
       </c>
       <c r="S28" s="1" t="inlineStr">
         <is>
@@ -2362,31 +2362,31 @@
         <v>-18.216815</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.904775</v>
+        <v>-5.895978</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.690294</v>
+        <v>-1.683608</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.375884</v>
+        <v>-1.36703</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.579922</v>
+        <v>-1.565896</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.7873790000000001</v>
+        <v>-0.772412</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.131082</v>
+        <v>-4.112893</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.010263</v>
+        <v>-4.887812</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.488824</v>
+        <v>-2.372995</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.551473</v>
+        <v>-2.45641</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.17902</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -6907,34 +6907,34 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.008796999999999999</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.006686</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.008854000000000001</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.014026</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.014967</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.018189</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.122451</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.115829</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.09506299999999999</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.078457</v>
       </c>
     </row>
     <row r="101">
@@ -29958,7 +29958,11 @@
           <t>Depreciation of property and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -32492,7 +32496,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -33754,7 +33762,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -44152,7 +44164,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -57332,7 +57344,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -59904,7 +59920,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E486" t="inlineStr">
         <is>
           <t>-</t>
@@ -62802,7 +62822,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NBY.xlsx
+++ b/output/pdf_financials_xlsx/NBY.xlsx
@@ -1439,10 +1439,10 @@
         <v>6.726809</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.267036</v>
+        <v>-0.267036</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.195188</v>
+        <v>-0.195188</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.008259000000000001</v>
@@ -4632,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.615107</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.736653</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>0</v>
@@ -7771,13 +7771,13 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-5.599779</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.66232</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-1.705403</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -33126,7 +33126,11 @@
           <t>Flow-through share units issued pursuant to a private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -33230,7 +33234,11 @@
           <t>Units issued pursuant to a private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -34600,7 +34608,11 @@
           <t>Units issued pursuant to a private placement (Note 13)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -34706,7 +34718,11 @@
           <t>Flow-through share units issued pursuant to a private placement (Note 13)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -36608,7 +36624,11 @@
           <t>Private placements (Note 9)</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -39128,7 +39148,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -40170,7 +40194,11 @@
           <t>Private placements (Note 7)</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -41658,7 +41686,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -45530,7 +45562,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -46274,7 +46310,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -48166,7 +48206,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -49652,7 +49696,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -74022,7 +74070,11 @@
           <t>Deferred income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E621" t="inlineStr">
         <is>
           <t>-</t>
